--- a/Lora_and_SigFox_Devices/MeteoWind_IoT_Pro_Gen2/Customer_uplinks_downlinks_wind.xlsx
+++ b/Lora_and_SigFox_Devices/MeteoWind_IoT_Pro_Gen2/Customer_uplinks_downlinks_wind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Documents\GitHub\FW_MeteoWind_IoT_Pro_Gen2\zDOC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Desktop\uplinks downlinks Gen2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1444BAC5-490D-476D-8764-12F9C894402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F3B8DC-6FC3-415F-936F-553EA2E828FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>UPLINKS</t>
   </si>
@@ -72,9 +72,21 @@
     <t xml:space="preserve">Port </t>
   </si>
   <si>
+    <t>Example - in HEX</t>
+  </si>
+  <si>
     <t>Byte 0</t>
   </si>
   <si>
+    <t>Byte 1</t>
+  </si>
+  <si>
+    <t>Byte 2</t>
+  </si>
+  <si>
+    <t>Byte 3</t>
+  </si>
+  <si>
     <t>O1O2O3</t>
   </si>
   <si>
@@ -120,6 +132,12 @@
     <t>O1O2O3O4</t>
   </si>
   <si>
+    <t>O1-delay</t>
+  </si>
+  <si>
+    <t>O2O3O4 - packets, minimum is O1O2, delay and 1 packet number</t>
+  </si>
+  <si>
     <t>Retrans old Alarm payload request</t>
   </si>
   <si>
@@ -129,9 +147,21 @@
     <t>Service Message Request port</t>
   </si>
   <si>
+    <t xml:space="preserve">O1- request service message. </t>
+  </si>
+  <si>
     <t>00 - MH0S Service message, 01 - MH1S Service message, 02 - MH2S</t>
   </si>
   <si>
+    <t>Change payload type</t>
+  </si>
+  <si>
+    <t>O1- payload type</t>
+  </si>
+  <si>
+    <t>O0 – Scalar, O1-Vector</t>
+  </si>
+  <si>
     <t>timesync 1 - absolute value</t>
   </si>
   <si>
@@ -153,16 +183,22 @@
     <t>O1 - delay, O2 - alarm packet Nr, 0..63</t>
   </si>
   <si>
+    <t>O1- change periodic payload period 2-10 min, in HEXA, 0A = 10 min</t>
+  </si>
+  <si>
+    <t>Rejoin switch and counter</t>
+  </si>
+  <si>
     <t>O1 - reset if argument is 1, reset will be performed after 60 seconds of downlink</t>
   </si>
   <si>
-    <t>Example Data - in HEX</t>
-  </si>
-  <si>
-    <t>O2O3O4 - packets, minimum is O1O2, O1 - delay and O2 packet number if only one packet is needed</t>
-  </si>
-  <si>
-    <t>O1- change periodic payload period 2-10 min, in HEXA, so 0A = 10 min</t>
+    <t>Timesync</t>
+  </si>
+  <si>
+    <t>01 - switch 00 OFF, 01 ON, 02 get config to port 50, 0203 - counter after that messages will be rejoin performed, from 5 to 4095, default = OFF</t>
+  </si>
+  <si>
+    <t>O1O2 - counter from 5 to 4095, when can be timesync, default = 1000</t>
   </si>
 </sst>
 </file>
@@ -210,6 +246,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00A933"/>
         <bgColor rgb="FF008000"/>
       </patternFill>
@@ -226,12 +268,6 @@
         <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF008000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -245,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -258,27 +294,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,14 +580,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G30"/>
+  <dimension ref="A2:G33"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54" style="2" customWidth="1"/>
-    <col min="4" max="4" width="111.140625" style="2" customWidth="1"/>
-    <col min="5" max="7" width="26.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="2" customWidth="1"/>
+    <col min="4" max="7" width="26.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.35">
@@ -562,71 +601,73 @@
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="18"/>
-      <c r="E5" s="17"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>50</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
@@ -643,244 +684,301 @@
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="D11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="A15" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>100</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>15</v>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>103</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>18</v>
+      <c r="B17" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>104</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>21</v>
+      <c r="B18" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>107</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>108</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>25</v>
+      <c r="B20" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>109</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>27</v>
+      <c r="B21" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>110</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>28</v>
+      <c r="B22" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="A23" s="1">
+        <v>111</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="A24" s="1">
+        <v>112</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>120</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="B27" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+      <c r="C27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
+        <v>121</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>130</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>132</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="B32" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
